--- a/data/trans_orig/IP05A05-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP05A05-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16616</t>
+          <t>16247</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30200</t>
+          <t>30822</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17565</t>
+          <t>17494</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33454</t>
+          <t>32518</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37703</t>
+          <t>38254</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59108</t>
+          <t>58791</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69727</t>
+          <t>70475</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89290</t>
+          <t>89380</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>76553</t>
+          <t>76181</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97014</t>
+          <t>96469</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>154153</t>
+          <t>152636</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>180244</t>
+          <t>180871</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,27%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28297</t>
+          <t>27908</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45038</t>
+          <t>44823</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31580</t>
+          <t>32327</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48709</t>
+          <t>49461</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63954</t>
+          <t>64505</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>87581</t>
+          <t>89561</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38872</t>
+          <t>37931</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>57023</t>
+          <t>57684</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53924</t>
+          <t>53955</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>74981</t>
+          <t>74694</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>97891</t>
+          <t>98021</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>125868</t>
+          <t>124926</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91245</t>
+          <t>91221</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>113416</t>
+          <t>113868</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91832</t>
+          <t>91763</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>114588</t>
+          <t>113473</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>189989</t>
+          <t>189459</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>221294</t>
+          <t>222184</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,8%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36084</t>
+          <t>35582</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53847</t>
+          <t>53789</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35627</t>
+          <t>35875</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53835</t>
+          <t>53590</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75927</t>
+          <t>75500</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101864</t>
+          <t>102480</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39619</t>
+          <t>40295</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57062</t>
+          <t>58735</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41042</t>
+          <t>40358</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>58806</t>
+          <t>58737</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>85732</t>
+          <t>85700</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>110983</t>
+          <t>109992</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,32%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62205</t>
+          <t>61459</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79845</t>
+          <t>80238</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66854</t>
+          <t>67457</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85449</t>
+          <t>86996</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>133347</t>
+          <t>134925</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>160241</t>
+          <t>160538</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,93%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12514</t>
+          <t>12665</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25008</t>
+          <t>24962</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17543</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31470</t>
+          <t>30766</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33186</t>
+          <t>33059</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51638</t>
+          <t>51659</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70078</t>
+          <t>71793</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>95270</t>
+          <t>96673</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70474</t>
+          <t>71119</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93464</t>
+          <t>94383</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>148560</t>
+          <t>149454</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>181574</t>
+          <t>182021</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,64%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>82036</t>
+          <t>79610</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>106216</t>
+          <t>104029</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>81916</t>
+          <t>80869</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>105833</t>
+          <t>103930</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>169089</t>
+          <t>169649</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>202486</t>
+          <t>202680</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,59%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25401</t>
+          <t>25484</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43188</t>
+          <t>43137</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24394</t>
+          <t>24578</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41052</t>
+          <t>41439</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>54528</t>
+          <t>53966</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>79610</t>
+          <t>78179</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>181875</t>
+          <t>184998</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>222101</t>
+          <t>223248</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>201392</t>
+          <t>199954</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>238770</t>
+          <t>239758</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>396081</t>
+          <t>390977</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>452505</t>
+          <t>448218</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,01%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>325203</t>
+          <t>323204</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367357</t>
+          <t>365301</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>337960</t>
+          <t>339142</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>380237</t>
+          <t>380793</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>675488</t>
+          <t>678822</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>736998</t>
+          <t>740350</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,88%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>115426</t>
+          <t>113549</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>151137</t>
+          <t>148841</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,47 +2798,47 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>16,71%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>21,91%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>140349</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>122456</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>157361</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>19,47%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
           <t>16,99%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>22,25%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>140349</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>122813</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>157003</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>19,47%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>17,04%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>247392</t>
+          <t>248684</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>295825</t>
+          <t>295430</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34824</t>
+          <t>35005</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53551</t>
+          <t>52830</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40502</t>
+          <t>40942</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61156</t>
+          <t>60500</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80947</t>
+          <t>79709</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107009</t>
+          <t>106762</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,31%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44706</t>
+          <t>43725</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63374</t>
+          <t>62688</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49502</t>
+          <t>48789</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69868</t>
+          <t>69516</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98871</t>
+          <t>99953</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>125762</t>
+          <t>127610</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>43,4%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33047</t>
+          <t>33539</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51064</t>
+          <t>52177</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36259</t>
+          <t>36607</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55895</t>
+          <t>56218</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>74869</t>
+          <t>74533</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>101543</t>
+          <t>100861</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,3%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72696</t>
+          <t>74406</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94225</t>
+          <t>95811</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71015</t>
+          <t>69542</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93527</t>
+          <t>92914</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>149804</t>
+          <t>149934</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>181170</t>
+          <t>182735</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,48%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72188</t>
+          <t>72169</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>96505</t>
+          <t>94586</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93414</t>
+          <t>93762</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>117625</t>
+          <t>118682</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>172002</t>
+          <t>171148</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>204719</t>
+          <t>205097</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,68%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30845</t>
+          <t>31231</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50208</t>
+          <t>49289</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28734</t>
+          <t>27278</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47184</t>
+          <t>45586</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63478</t>
+          <t>63868</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89303</t>
+          <t>89578</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39717</t>
+          <t>39901</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57645</t>
+          <t>57385</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34048</t>
+          <t>34127</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52043</t>
+          <t>52029</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>77966</t>
+          <t>77545</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>102721</t>
+          <t>103582</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62634</t>
+          <t>62337</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82242</t>
+          <t>82243</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79827</t>
+          <t>79688</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99573</t>
+          <t>99824</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>147458</t>
+          <t>146592</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>176241</t>
+          <t>174319</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,14%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27402</t>
+          <t>27751</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44423</t>
+          <t>43606</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27166</t>
+          <t>27105</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43372</t>
+          <t>43270</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58536</t>
+          <t>59226</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>82676</t>
+          <t>81529</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,32%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50538</t>
+          <t>50002</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>72842</t>
+          <t>73537</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44238</t>
+          <t>44538</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65377</t>
+          <t>66053</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99742</t>
+          <t>100166</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>129750</t>
+          <t>131519</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,53%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80340</t>
+          <t>79786</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>105316</t>
+          <t>103255</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>84496</t>
+          <t>83517</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>107436</t>
+          <t>108064</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>170322</t>
+          <t>170788</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>204305</t>
+          <t>206356</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,47%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45362</t>
+          <t>46184</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>67812</t>
+          <t>66792</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>48659</t>
+          <t>47255</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69451</t>
+          <t>70238</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>101138</t>
+          <t>100376</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>132898</t>
+          <t>131499</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,52%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>216955</t>
+          <t>216147</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>257434</t>
+          <t>257005</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>209951</t>
+          <t>207304</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>251673</t>
+          <t>248364</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>434606</t>
+          <t>438833</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>492009</t>
+          <t>497001</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,96%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>277893</t>
+          <t>280953</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>321051</t>
+          <t>323387</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>322864</t>
+          <t>327484</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>369822</t>
+          <t>371013</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>620186</t>
+          <t>620180</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>678075</t>
+          <t>683128</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,68%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>153685</t>
+          <t>154053</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>190977</t>
+          <t>193515</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>156540</t>
+          <t>156655</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>195624</t>
+          <t>195820</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>322924</t>
+          <t>320982</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>376364</t>
+          <t>375092</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44067</t>
+          <t>44552</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63325</t>
+          <t>63768</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39771</t>
+          <t>40305</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60622</t>
+          <t>60895</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>91069</t>
+          <t>91072</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>118332</t>
+          <t>119275</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,43%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27673</t>
+          <t>27403</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45927</t>
+          <t>45724</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35188</t>
+          <t>35001</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54657</t>
+          <t>54634</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68588</t>
+          <t>68114</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>93461</t>
+          <t>94655</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,67%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33631</t>
+          <t>33961</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51539</t>
+          <t>52280</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44001</t>
+          <t>43762</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63521</t>
+          <t>63109</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>82458</t>
+          <t>82754</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>109590</t>
+          <t>108842</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,72%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>70922</t>
+          <t>71176</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92860</t>
+          <t>92637</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>83302</t>
+          <t>82951</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107301</t>
+          <t>106859</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>162876</t>
+          <t>162048</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>194165</t>
+          <t>194081</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,02%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70437</t>
+          <t>70692</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>92430</t>
+          <t>92126</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>73999</t>
+          <t>74827</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>97519</t>
+          <t>97730</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>150652</t>
+          <t>151671</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>183252</t>
+          <t>183958</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,68%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33886</t>
+          <t>34176</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52155</t>
+          <t>52619</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34872</t>
+          <t>34601</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53419</t>
+          <t>53721</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73814</t>
+          <t>74041</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99630</t>
+          <t>100273</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43061</t>
+          <t>41941</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61440</t>
+          <t>60278</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42666</t>
+          <t>42555</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61869</t>
+          <t>62040</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>89774</t>
+          <t>88757</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>116214</t>
+          <t>115317</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,74%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60948</t>
+          <t>62107</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80566</t>
+          <t>82288</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63578</t>
+          <t>64584</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84799</t>
+          <t>84302</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>133067</t>
+          <t>132894</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>163373</t>
+          <t>162282</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,29%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25801</t>
+          <t>26377</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41518</t>
+          <t>42579</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32063</t>
+          <t>32251</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50566</t>
+          <t>48583</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>61993</t>
+          <t>62679</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>84746</t>
+          <t>85602</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,53%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70648</t>
+          <t>70496</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>94190</t>
+          <t>93436</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67532</t>
+          <t>65991</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90584</t>
+          <t>89550</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>143594</t>
+          <t>143762</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>177798</t>
+          <t>176596</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>42,94%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80451</t>
+          <t>80012</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>105160</t>
+          <t>104621</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75535</t>
+          <t>75887</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>100050</t>
+          <t>100358</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>163606</t>
+          <t>164106</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>197155</t>
+          <t>197808</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>48,1%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22652</t>
+          <t>23052</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40715</t>
+          <t>40550</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30874</t>
+          <t>30650</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49996</t>
+          <t>49694</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>58844</t>
+          <t>58311</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>83351</t>
+          <t>83443</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,29%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249014</t>
+          <t>248773</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>290055</t>
+          <t>292226</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253670</t>
+          <t>252629</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>297778</t>
+          <t>296964</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>516380</t>
+          <t>515515</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>575268</t>
+          <t>575406</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,79%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>262204</t>
+          <t>261132</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>303627</t>
+          <t>302847</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>270102</t>
+          <t>270678</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>313867</t>
+          <t>314509</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>546295</t>
+          <t>543964</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>604179</t>
+          <t>603837</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,76%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>133926</t>
+          <t>133665</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>168328</t>
+          <t>167702</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>158460</t>
+          <t>158795</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>196834</t>
+          <t>196631</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>301096</t>
+          <t>301763</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>352918</t>
+          <t>351347</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>106333</t>
+          <t>105772</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114515</t>
+          <t>114405</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>126402</t>
+          <t>126728</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>136836</t>
+          <t>136652</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>236391</t>
+          <t>236613</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>249358</t>
+          <t>249513</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9788</t>
+          <t>10032</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14789</t>
+          <t>15127</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>379</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>7875</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10846</t>
+          <t>9442</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>138125</t>
+          <t>137980</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>164065</t>
+          <t>164645</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>206725</t>
+          <t>205744</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>227612</t>
+          <t>227868</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>352314</t>
+          <t>353628</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>386815</t>
+          <t>386735</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,8%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12608</t>
+          <t>12071</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38737</t>
+          <t>40433</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15114</t>
+          <t>15008</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32458</t>
+          <t>32374</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>32434</t>
+          <t>32882</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>63283</t>
+          <t>64815</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9345</t>
+          <t>9423</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23047</t>
+          <t>22015</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>8620</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21950</t>
+          <t>22652</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22090</t>
+          <t>20969</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39678</t>
+          <t>40011</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>71927</t>
+          <t>65440</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>141802</t>
+          <t>140826</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>118016</t>
+          <t>117748</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>142515</t>
+          <t>142937</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>180488</t>
+          <t>183123</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>275183</t>
+          <t>272423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>72,51%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35185</t>
+          <t>36071</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111091</t>
+          <t>119024</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28104</t>
+          <t>28109</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50340</t>
+          <t>51083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71726</t>
+          <t>73975</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>171982</t>
+          <t>170097</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,28%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19874</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10443</t>
+          <t>10441</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25226</t>
+          <t>25739</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19318</t>
+          <t>18976</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39413</t>
+          <t>38983</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>102409</t>
+          <t>102213</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>122785</t>
+          <t>123117</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>106708</t>
+          <t>105343</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>129215</t>
+          <t>128549</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>215773</t>
+          <t>215598</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>245147</t>
+          <t>246077</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,95%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23698</t>
+          <t>23355</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40164</t>
+          <t>40727</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25707</t>
+          <t>26270</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46200</t>
+          <t>46171</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54745</t>
+          <t>53825</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>79607</t>
+          <t>80327</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14743</t>
+          <t>14670</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30486</t>
+          <t>30679</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36472</t>
+          <t>36700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>38643</t>
+          <t>38579</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>61347</t>
+          <t>61209</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>431590</t>
+          <t>433761</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>525962</t>
+          <t>527522</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>580265</t>
+          <t>579026</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>622231</t>
+          <t>622807</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1031056</t>
+          <t>1032372</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1135895</t>
+          <t>1132857</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,49%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>87395</t>
+          <t>86040</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>191695</t>
+          <t>194931</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>84286</t>
+          <t>82847</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>119746</t>
+          <t>119506</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>181009</t>
+          <t>181538</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>301988</t>
+          <t>282317</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39718</t>
+          <t>39649</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63702</t>
+          <t>64793</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46894</t>
+          <t>48013</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>74088</t>
+          <t>75794</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>91608</t>
+          <t>94428</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>129732</t>
+          <t>130997</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
